--- a/TPASS/TPASS表格.xlsx
+++ b/TPASS/TPASS表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\運籌\115\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBC6AEF-169B-465F-974D-9E9D3B243A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD3FE81-7BC7-43B0-8988-F2DDA16FA75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="花蓮縣TPASS年占比" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="臺東縣公路客運TPASS年占比" sheetId="10" r:id="rId10"/>
     <sheet name="花蓮縣公路客運TPASS月占比" sheetId="11" r:id="rId11"/>
     <sheet name="臺東縣公路客運TPASS月占比" sheetId="12" r:id="rId12"/>
+    <sheet name="市區客運各種TPASS成長率" sheetId="13" r:id="rId13"/>
+    <sheet name="公路客運各種TPASS成長率" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>year</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -157,6 +159,30 @@
   </si>
   <si>
     <t>臺東縣公路客運TPASS每月筆數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#HUA-199</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#HUA-399</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>#TTT-299</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113成長率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114成長率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">票種次類型 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1589,6 +1615,246 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B56D183-E054-4F52-B242-86CC9E24C27F}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1">
+        <v>112</v>
+      </c>
+      <c r="C1">
+        <v>113</v>
+      </c>
+      <c r="D1">
+        <v>114</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>12205</v>
+      </c>
+      <c r="C2">
+        <v>47332</v>
+      </c>
+      <c r="D2">
+        <v>85367</v>
+      </c>
+      <c r="E2" s="1">
+        <f>(C2-B2)/B2</f>
+        <v>2.8780827529700943</v>
+      </c>
+      <c r="F2" s="1">
+        <f>(D2-C2)/C2</f>
+        <v>0.80357897405560719</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>1828</v>
+      </c>
+      <c r="C3">
+        <v>9260</v>
+      </c>
+      <c r="D3">
+        <v>13203</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E4" si="0">(C3-B3)/B3</f>
+        <v>4.0656455142231946</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F4" si="1">(D3-C3)/C3</f>
+        <v>0.42580993520518357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>4071</v>
+      </c>
+      <c r="C4">
+        <v>20893</v>
+      </c>
+      <c r="D4">
+        <v>29947</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
+        <v>4.1321542618521248</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="1"/>
+        <v>0.43335088307088498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2,B3,B4)</f>
+        <v>18104</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:D5" si="2">SUM(C2,C3,C4)</f>
+        <v>77485</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>128517</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E70FCB4-A082-4C88-86B5-EBE994486089}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1">
+        <v>112</v>
+      </c>
+      <c r="C1">
+        <v>113</v>
+      </c>
+      <c r="D1">
+        <v>114</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="e">
+        <f>(C2-B2)/B2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F2" s="1" t="e">
+        <f>(D2-C2)/C2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>8894</v>
+      </c>
+      <c r="C3">
+        <v>68052</v>
+      </c>
+      <c r="D3">
+        <v>62058</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:F4" si="0">(C3-B3)/B3</f>
+        <v>6.6514504160107935</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="0"/>
+        <v>-8.8079703755951325E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>71307</v>
+      </c>
+      <c r="C4">
+        <v>298068</v>
+      </c>
+      <c r="D4">
+        <v>330869</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
+        <v>3.1800664731372796</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>0.11004535877719178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2,B3,B4)</f>
+        <v>80201</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:D5" si="1">SUM(C2,C3,C4)</f>
+        <v>366120</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>392929</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA1AE27-E43F-415B-8043-BB7EC61E8EAC}">
   <dimension ref="A1:D5"/>

--- a/TPASS/TPASS表格.xlsx
+++ b/TPASS/TPASS表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\運籌\115\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD3FE81-7BC7-43B0-8988-F2DDA16FA75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6381AD2F-8B92-46F0-A8DC-BD7D0C0098F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="13" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="花蓮縣TPASS年占比" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,10 @@
     <sheet name="臺東縣公路客運TPASS月占比" sheetId="12" r:id="rId12"/>
     <sheet name="市區客運各種TPASS成長率" sheetId="13" r:id="rId13"/>
     <sheet name="公路客運各種TPASS成長率" sheetId="14" r:id="rId14"/>
+    <sheet name="花蓮縣市區客運平均搭乘里程" sheetId="15" r:id="rId15"/>
+    <sheet name="臺東縣市區客運平均搭乘里程" sheetId="16" r:id="rId16"/>
+    <sheet name="花蓮縣公路客運平均搭乘里程" sheetId="17" r:id="rId17"/>
+    <sheet name="臺東縣公路客運平均搭乘里程" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="39">
   <si>
     <t>year</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -185,14 +189,39 @@
     <t xml:space="preserve">票種次類型 </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>year-month</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>該月資料總筆數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>該月有效里程筆數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>該月累積里程_公里</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>該月平均里程_公里</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -240,10 +269,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -714,7 +747,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -722,7 +755,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
@@ -1167,7 +1200,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -1175,7 +1208,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>25</v>
@@ -1855,6 +1888,1602 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102248B0-3889-4A26-BFAD-CBA42138285B}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45444</v>
+      </c>
+      <c r="B2">
+        <v>24926</v>
+      </c>
+      <c r="C2">
+        <v>21987</v>
+      </c>
+      <c r="D2" s="3">
+        <v>391603</v>
+      </c>
+      <c r="E2" s="5">
+        <f>D2/C2</f>
+        <v>17.810660845044801</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45474</v>
+      </c>
+      <c r="B3">
+        <v>20223</v>
+      </c>
+      <c r="C3">
+        <v>17913</v>
+      </c>
+      <c r="D3" s="3">
+        <v>303016</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E20" si="0">D3/C3</f>
+        <v>16.915982805783511</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45505</v>
+      </c>
+      <c r="B4">
+        <v>25505</v>
+      </c>
+      <c r="C4">
+        <v>22794</v>
+      </c>
+      <c r="D4" s="3">
+        <v>414230</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>18.17276476265684</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45536</v>
+      </c>
+      <c r="B5">
+        <v>35607</v>
+      </c>
+      <c r="C5">
+        <v>32269</v>
+      </c>
+      <c r="D5" s="3">
+        <v>568299</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>17.611298769717067</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45566</v>
+      </c>
+      <c r="B6">
+        <v>32885</v>
+      </c>
+      <c r="C6">
+        <v>29943</v>
+      </c>
+      <c r="D6" s="3">
+        <v>526001</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>17.566743479277292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="B7">
+        <v>35102</v>
+      </c>
+      <c r="C7">
+        <v>34628</v>
+      </c>
+      <c r="D7" s="3">
+        <v>528955</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>15.275355203881253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45627</v>
+      </c>
+      <c r="B8">
+        <v>39126</v>
+      </c>
+      <c r="C8">
+        <v>38801</v>
+      </c>
+      <c r="D8" s="3">
+        <v>628069</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>16.186928171954332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B9">
+        <v>21424</v>
+      </c>
+      <c r="C9">
+        <v>21233</v>
+      </c>
+      <c r="D9" s="3">
+        <v>282008</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>13.281589977864645</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B10">
+        <v>21922</v>
+      </c>
+      <c r="C10">
+        <v>21767</v>
+      </c>
+      <c r="D10" s="3">
+        <v>294587</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>13.533651858317636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45717</v>
+      </c>
+      <c r="B11">
+        <v>29047</v>
+      </c>
+      <c r="C11">
+        <v>28744</v>
+      </c>
+      <c r="D11" s="3">
+        <v>381056</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>13.256888394099638</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45748</v>
+      </c>
+      <c r="B12">
+        <v>29161</v>
+      </c>
+      <c r="C12">
+        <v>28715</v>
+      </c>
+      <c r="D12" s="3">
+        <v>381626</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>13.290127111265889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45778</v>
+      </c>
+      <c r="B13">
+        <v>27933</v>
+      </c>
+      <c r="C13">
+        <v>27487</v>
+      </c>
+      <c r="D13" s="3">
+        <v>330730</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>12.032233419434641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45809</v>
+      </c>
+      <c r="B14">
+        <v>26215</v>
+      </c>
+      <c r="C14">
+        <v>25734</v>
+      </c>
+      <c r="D14" s="3">
+        <v>345893</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>13.441089609077485</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B15">
+        <v>20419</v>
+      </c>
+      <c r="C15">
+        <v>20196</v>
+      </c>
+      <c r="D15" s="3">
+        <v>255285</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>12.640374331550802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B16">
+        <v>21356</v>
+      </c>
+      <c r="C16">
+        <v>21090</v>
+      </c>
+      <c r="D16" s="3">
+        <v>279581</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>13.256567093409199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B17">
+        <v>30418</v>
+      </c>
+      <c r="C17">
+        <v>30135</v>
+      </c>
+      <c r="D17" s="3">
+        <v>401887</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>13.336220341795254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B18">
+        <v>31010</v>
+      </c>
+      <c r="C18">
+        <v>30644</v>
+      </c>
+      <c r="D18" s="3">
+        <v>402092</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>13.121394073880694</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B19">
+        <v>26744</v>
+      </c>
+      <c r="C19">
+        <v>25905</v>
+      </c>
+      <c r="D19" s="3">
+        <v>305031</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>11.774985524030111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B20">
+        <v>29858</v>
+      </c>
+      <c r="C20">
+        <v>28854</v>
+      </c>
+      <c r="D20" s="3">
+        <v>339844</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>11.778055035696957</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21">
+        <f>SUM(B2:B20)</f>
+        <v>528881</v>
+      </c>
+      <c r="C21">
+        <f>SUM(C2:C20)</f>
+        <v>508839</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <f>(B21-C21)/B21</f>
+        <v>3.7895103057209466E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51D32AC-971C-4ECF-8B2B-AD4356D727D8}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45444</v>
+      </c>
+      <c r="B2">
+        <v>11505</v>
+      </c>
+      <c r="C2">
+        <v>10717</v>
+      </c>
+      <c r="D2" s="3">
+        <v>82922</v>
+      </c>
+      <c r="E2" s="5">
+        <f>D2/C2</f>
+        <v>7.7374265186152842</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45474</v>
+      </c>
+      <c r="B3">
+        <v>11343</v>
+      </c>
+      <c r="C3">
+        <v>10618</v>
+      </c>
+      <c r="D3" s="3">
+        <v>84740</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E20" si="0">D3/C3</f>
+        <v>7.9807873422490108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45505</v>
+      </c>
+      <c r="B4">
+        <v>14507</v>
+      </c>
+      <c r="C4">
+        <v>13559</v>
+      </c>
+      <c r="D4" s="3">
+        <v>109263</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>8.0583376355188427</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45536</v>
+      </c>
+      <c r="B5">
+        <v>13917</v>
+      </c>
+      <c r="C5">
+        <v>12985</v>
+      </c>
+      <c r="D5" s="3">
+        <v>96513</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4326530612244897</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45566</v>
+      </c>
+      <c r="B6">
+        <v>12989</v>
+      </c>
+      <c r="C6">
+        <v>12090</v>
+      </c>
+      <c r="D6" s="3">
+        <v>88982</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3599669148056241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="B7">
+        <v>15461</v>
+      </c>
+      <c r="C7">
+        <v>14230</v>
+      </c>
+      <c r="D7" s="3">
+        <v>98567</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>6.9267041461700636</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45627</v>
+      </c>
+      <c r="B8">
+        <v>13546</v>
+      </c>
+      <c r="C8">
+        <v>11448</v>
+      </c>
+      <c r="D8" s="3">
+        <v>76919</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>6.7189902166317257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B9">
+        <v>10810</v>
+      </c>
+      <c r="C9">
+        <v>9468</v>
+      </c>
+      <c r="D9" s="3">
+        <v>63373</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>6.6933882551753277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B10">
+        <v>9961</v>
+      </c>
+      <c r="C10">
+        <v>8557</v>
+      </c>
+      <c r="D10" s="3">
+        <v>59076</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>6.9038214327451213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45717</v>
+      </c>
+      <c r="B11">
+        <v>12037</v>
+      </c>
+      <c r="C11">
+        <v>10195</v>
+      </c>
+      <c r="D11" s="3">
+        <v>70899</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>6.9542913192741542</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45748</v>
+      </c>
+      <c r="B12">
+        <v>14114</v>
+      </c>
+      <c r="C12">
+        <v>12358</v>
+      </c>
+      <c r="D12" s="3">
+        <v>92394</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4764525004045961</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45778</v>
+      </c>
+      <c r="B13">
+        <v>14616</v>
+      </c>
+      <c r="C13">
+        <v>12703</v>
+      </c>
+      <c r="D13" s="3">
+        <v>95452</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>7.5141305203495241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45809</v>
+      </c>
+      <c r="B14">
+        <v>14883</v>
+      </c>
+      <c r="C14">
+        <v>13075</v>
+      </c>
+      <c r="D14" s="3">
+        <v>100325</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>7.6730401529636714</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B15">
+        <v>12631</v>
+      </c>
+      <c r="C15">
+        <v>11756</v>
+      </c>
+      <c r="D15" s="3">
+        <v>89764</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>7.6355903368492681</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B16">
+        <v>14055</v>
+      </c>
+      <c r="C16">
+        <v>13197</v>
+      </c>
+      <c r="D16" s="3">
+        <v>104351</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>7.9071758733045385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B17">
+        <v>11219</v>
+      </c>
+      <c r="C17">
+        <v>10233</v>
+      </c>
+      <c r="D17" s="3">
+        <v>76978</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>7.5225251636861135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B18">
+        <v>13730</v>
+      </c>
+      <c r="C18">
+        <v>12205</v>
+      </c>
+      <c r="D18" s="3">
+        <v>91341</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4839000409668168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B19">
+        <v>11433</v>
+      </c>
+      <c r="C19">
+        <v>11433</v>
+      </c>
+      <c r="D19" s="3">
+        <v>84203</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3649085979183067</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B20">
+        <v>13272</v>
+      </c>
+      <c r="C20">
+        <v>13272</v>
+      </c>
+      <c r="D20" s="3">
+        <v>93851</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>7.0713532248342377</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <f>SUM(B2:B20)</f>
+        <v>246029</v>
+      </c>
+      <c r="C21">
+        <f>SUM(C2:C20)</f>
+        <v>224099</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <f>(B21-C21)/B21</f>
+        <v>8.9135833580594154E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BF4100-5575-448C-AA06-7EFDF070E657}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45444</v>
+      </c>
+      <c r="B2">
+        <v>27271</v>
+      </c>
+      <c r="C2">
+        <v>23556</v>
+      </c>
+      <c r="D2" s="3">
+        <v>518742</v>
+      </c>
+      <c r="E2" s="5">
+        <f>D2/C2</f>
+        <v>22.021650534895567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45474</v>
+      </c>
+      <c r="B3">
+        <v>23860</v>
+      </c>
+      <c r="C3">
+        <v>20320</v>
+      </c>
+      <c r="D3" s="3">
+        <v>466888</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E20" si="0">D3/C3</f>
+        <v>22.976771653543306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45505</v>
+      </c>
+      <c r="B4">
+        <v>26190</v>
+      </c>
+      <c r="C4">
+        <v>22595</v>
+      </c>
+      <c r="D4" s="3">
+        <v>518428</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>22.944368223058198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45536</v>
+      </c>
+      <c r="B5">
+        <v>52390</v>
+      </c>
+      <c r="C5">
+        <v>48277</v>
+      </c>
+      <c r="D5" s="3">
+        <v>977191</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>20.241336454212149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45566</v>
+      </c>
+      <c r="B6">
+        <v>27791</v>
+      </c>
+      <c r="C6">
+        <v>25458</v>
+      </c>
+      <c r="D6" s="3">
+        <v>529279</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>20.790282033152643</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="B7">
+        <v>60495</v>
+      </c>
+      <c r="C7">
+        <v>54627</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1059598</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>19.396964870851409</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45627</v>
+      </c>
+      <c r="B8">
+        <v>54204</v>
+      </c>
+      <c r="C8">
+        <v>49966</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1022721</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>20.468338470159708</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B9">
+        <v>25166</v>
+      </c>
+      <c r="C9">
+        <v>23228</v>
+      </c>
+      <c r="D9" s="3">
+        <v>522471</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>22.493154813156536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B10">
+        <v>24706</v>
+      </c>
+      <c r="C10">
+        <v>23208</v>
+      </c>
+      <c r="D10" s="3">
+        <v>519551</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>22.386720096518442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45717</v>
+      </c>
+      <c r="B11">
+        <v>31262</v>
+      </c>
+      <c r="C11">
+        <v>29390</v>
+      </c>
+      <c r="D11" s="3">
+        <v>629968</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>21.434773732562096</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45748</v>
+      </c>
+      <c r="B12">
+        <v>32846</v>
+      </c>
+      <c r="C12">
+        <v>30880</v>
+      </c>
+      <c r="D12" s="3">
+        <v>667683</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>21.621858808290156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45778</v>
+      </c>
+      <c r="B13">
+        <v>30858</v>
+      </c>
+      <c r="C13">
+        <v>29204</v>
+      </c>
+      <c r="D13" s="3">
+        <v>623062</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>21.334817148335844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45809</v>
+      </c>
+      <c r="B14">
+        <v>29024</v>
+      </c>
+      <c r="C14">
+        <v>27301</v>
+      </c>
+      <c r="D14" s="3">
+        <v>605388</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>22.174572359986815</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B15">
+        <v>27565</v>
+      </c>
+      <c r="C15">
+        <v>25595</v>
+      </c>
+      <c r="D15" s="3">
+        <v>593083</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>23.171830435631961</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B16">
+        <v>28361</v>
+      </c>
+      <c r="C16">
+        <v>26275</v>
+      </c>
+      <c r="D16" s="3">
+        <v>607705</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>23.128639391056137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B17">
+        <v>30017</v>
+      </c>
+      <c r="C17">
+        <v>28306</v>
+      </c>
+      <c r="D17" s="3">
+        <v>591175</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>20.885148025153679</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B18">
+        <v>31646</v>
+      </c>
+      <c r="C18">
+        <v>29858</v>
+      </c>
+      <c r="D18" s="3">
+        <v>618273</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>20.707113671377854</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B19">
+        <v>26103</v>
+      </c>
+      <c r="C19">
+        <v>24688</v>
+      </c>
+      <c r="D19" s="3">
+        <v>507411</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>20.552940699935192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B20">
+        <v>31444</v>
+      </c>
+      <c r="C20">
+        <v>29869</v>
+      </c>
+      <c r="D20" s="3">
+        <v>624862</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>20.92008436840872</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <f>SUM(B2:B20)</f>
+        <v>621199</v>
+      </c>
+      <c r="C21">
+        <f>SUM(C2:C20)</f>
+        <v>572601</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <f>(B21-C21)/B21</f>
+        <v>7.8232579253991075E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507129D9-6C2B-4421-8F86-3B23A2D0C3AA}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45444</v>
+      </c>
+      <c r="B2">
+        <v>73129</v>
+      </c>
+      <c r="C2">
+        <v>65726</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1644016</v>
+      </c>
+      <c r="E2" s="5">
+        <f>D2/C2</f>
+        <v>25.013175912120012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45474</v>
+      </c>
+      <c r="B3">
+        <v>63277</v>
+      </c>
+      <c r="C3">
+        <v>56672</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1556817</v>
+      </c>
+      <c r="E3" s="5">
+        <f t="shared" ref="E3:E20" si="0">D3/C3</f>
+        <v>27.470655702992659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45505</v>
+      </c>
+      <c r="B4">
+        <v>77152</v>
+      </c>
+      <c r="C4">
+        <v>69582</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2071431</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="shared" si="0"/>
+        <v>29.769638699663705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45536</v>
+      </c>
+      <c r="B5">
+        <v>95063</v>
+      </c>
+      <c r="C5">
+        <v>86065</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2290371</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" si="0"/>
+        <v>26.612107128333236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45566</v>
+      </c>
+      <c r="B6">
+        <v>82314</v>
+      </c>
+      <c r="C6">
+        <v>76376</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1948796</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" si="0"/>
+        <v>25.515816486854508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="B7">
+        <v>100046</v>
+      </c>
+      <c r="C7">
+        <v>89386</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2287552</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>25.591837647953817</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45627</v>
+      </c>
+      <c r="B8">
+        <v>101854</v>
+      </c>
+      <c r="C8">
+        <v>92747</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2350506</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="0"/>
+        <v>25.34320247555177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B9">
+        <v>73346</v>
+      </c>
+      <c r="C9">
+        <v>68013</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1690189</v>
+      </c>
+      <c r="E9" s="5">
+        <f t="shared" si="0"/>
+        <v>24.850969667563554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45689</v>
+      </c>
+      <c r="B10">
+        <v>69857</v>
+      </c>
+      <c r="C10">
+        <v>64318</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1581770</v>
+      </c>
+      <c r="E10" s="5">
+        <f t="shared" si="0"/>
+        <v>24.592959980098883</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45717</v>
+      </c>
+      <c r="B11">
+        <v>87762</v>
+      </c>
+      <c r="C11">
+        <v>81109</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1924281</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>23.724629819132279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45748</v>
+      </c>
+      <c r="B12">
+        <v>132437</v>
+      </c>
+      <c r="C12">
+        <v>121791</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2581069</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>21.192608649243375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45778</v>
+      </c>
+      <c r="B13">
+        <v>82890</v>
+      </c>
+      <c r="C13">
+        <v>76764</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1801092</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>23.462716898546194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45809</v>
+      </c>
+      <c r="B14">
+        <v>79112</v>
+      </c>
+      <c r="C14">
+        <v>73249</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1826377</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>24.933814796106432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45839</v>
+      </c>
+      <c r="B15">
+        <v>62666</v>
+      </c>
+      <c r="C15">
+        <v>56924</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1495340</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>26.269060501721594</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45870</v>
+      </c>
+      <c r="B16">
+        <v>65423</v>
+      </c>
+      <c r="C16">
+        <v>59039</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1618685</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>27.417215738748961</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B17">
+        <v>79979</v>
+      </c>
+      <c r="C17">
+        <v>76719</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1791510</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>23.351581746373128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B18">
+        <v>89368</v>
+      </c>
+      <c r="C18">
+        <v>86717</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2048535</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="0"/>
+        <v>23.623222666835801</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B19">
+        <v>36204</v>
+      </c>
+      <c r="C19">
+        <v>34288</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1083525</v>
+      </c>
+      <c r="E19" s="5">
+        <f t="shared" si="0"/>
+        <v>31.600705786280916</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B20">
+        <v>89156</v>
+      </c>
+      <c r="C20">
+        <v>86967</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1929701</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>22.188887739027447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <f>SUM(B2:B20)</f>
+        <v>1541035</v>
+      </c>
+      <c r="C21">
+        <f>SUM(C2:C20)</f>
+        <v>1422452</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <f>(B21-C21)/B21</f>
+        <v>7.695023150025794E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA1AE27-E43F-415B-8043-BB7EC61E8EAC}">
   <dimension ref="A1:D5"/>
@@ -1953,15 +3582,15 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -2406,7 +4035,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -2414,7 +4043,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>9</v>
@@ -3045,7 +4674,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -3053,7 +4682,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>15</v>
@@ -3498,7 +5127,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -3506,7 +5135,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>17</v>

--- a/TPASS/TPASS表格.xlsx
+++ b/TPASS/TPASS表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\運籌\115\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6381AD2F-8B92-46F0-A8DC-BD7D0C0098F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD21005C-1598-4170-BB61-186AD7BE953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="13" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="16" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="花蓮縣TPASS年占比" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,10 @@
     <sheet name="臺東縣市區客運平均搭乘里程" sheetId="16" r:id="rId16"/>
     <sheet name="花蓮縣公路客運平均搭乘里程" sheetId="17" r:id="rId17"/>
     <sheet name="臺東縣公路客運平均搭乘里程" sheetId="18" r:id="rId18"/>
+    <sheet name="花蓮縣市區客運乘客各搭乘次數區間月人數變化表" sheetId="19" r:id="rId19"/>
+    <sheet name="工作表2" sheetId="20" r:id="rId20"/>
+    <sheet name="工作表3" sheetId="21" r:id="rId21"/>
+    <sheet name="工作表4" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="39">
   <si>
     <t>year</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3484,6 +3488,178 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A46D75-17CB-472B-82BD-D9CDF17017B0}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45444</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>45474</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>45505</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>45536</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>45566</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>45627</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>45658</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>45689</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>45717</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>45748</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>45778</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>45809</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>45839</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>45870</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>45901</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>45931</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>45962</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>45992</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <f>SUM(B2:B20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="6"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D29" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA1AE27-E43F-415B-8043-BB7EC61E8EAC}">
   <dimension ref="A1:D5"/>
@@ -3572,6 +3748,36 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7FBC57-2088-4E51-BD3D-2920E3DA2DBD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9903DFF-4878-4CA7-9CAB-60AB8A433796}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173477C9-8126-489F-A063-DCE4D38DDDFA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TPASS/TPASS表格.xlsx
+++ b/TPASS/TPASS表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\運籌\115\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\TPASS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD21005C-1598-4170-BB61-186AD7BE953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9B765F-04D3-4381-A728-7281AB38F5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="16" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="花蓮縣TPASS年占比" sheetId="1" r:id="rId1"/>
@@ -51,9 +51,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -273,12 +270,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -1900,8 +1896,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1914,7 +1909,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -1934,7 +1929,7 @@
       <c r="D2" s="3">
         <v>391603</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>17.810660845044801</v>
       </c>
@@ -1952,7 +1947,7 @@
       <c r="D3" s="3">
         <v>303016</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>16.915982805783511</v>
       </c>
@@ -1970,7 +1965,7 @@
       <c r="D4" s="3">
         <v>414230</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>18.17276476265684</v>
       </c>
@@ -1988,7 +1983,7 @@
       <c r="D5" s="3">
         <v>568299</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>17.611298769717067</v>
       </c>
@@ -2006,7 +2001,7 @@
       <c r="D6" s="3">
         <v>526001</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>17.566743479277292</v>
       </c>
@@ -2024,7 +2019,7 @@
       <c r="D7" s="3">
         <v>528955</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>15.275355203881253</v>
       </c>
@@ -2042,7 +2037,7 @@
       <c r="D8" s="3">
         <v>628069</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>16.186928171954332</v>
       </c>
@@ -2060,7 +2055,7 @@
       <c r="D9" s="3">
         <v>282008</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>13.281589977864645</v>
       </c>
@@ -2078,7 +2073,7 @@
       <c r="D10" s="3">
         <v>294587</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>13.533651858317636</v>
       </c>
@@ -2096,7 +2091,7 @@
       <c r="D11" s="3">
         <v>381056</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>13.256888394099638</v>
       </c>
@@ -2114,7 +2109,7 @@
       <c r="D12" s="3">
         <v>381626</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>13.290127111265889</v>
       </c>
@@ -2132,7 +2127,7 @@
       <c r="D13" s="3">
         <v>330730</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>12.032233419434641</v>
       </c>
@@ -2150,7 +2145,7 @@
       <c r="D14" s="3">
         <v>345893</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>13.441089609077485</v>
       </c>
@@ -2168,7 +2163,7 @@
       <c r="D15" s="3">
         <v>255285</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>12.640374331550802</v>
       </c>
@@ -2186,7 +2181,7 @@
       <c r="D16" s="3">
         <v>279581</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>13.256567093409199</v>
       </c>
@@ -2204,7 +2199,7 @@
       <c r="D17" s="3">
         <v>401887</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>13.336220341795254</v>
       </c>
@@ -2222,7 +2217,7 @@
       <c r="D18" s="3">
         <v>402092</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>13.121394073880694</v>
       </c>
@@ -2240,7 +2235,7 @@
       <c r="D19" s="3">
         <v>305031</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>11.774985524030111</v>
       </c>
@@ -2258,7 +2253,7 @@
       <c r="D20" s="3">
         <v>339844</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>11.778055035696957</v>
       </c>
@@ -2277,7 +2272,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>3.7895103057209466E-2</v>
       </c>
@@ -2299,8 +2294,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2313,7 +2307,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -2333,7 +2327,7 @@
       <c r="D2" s="3">
         <v>82922</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>7.7374265186152842</v>
       </c>
@@ -2351,7 +2345,7 @@
       <c r="D3" s="3">
         <v>84740</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>7.9807873422490108</v>
       </c>
@@ -2369,7 +2363,7 @@
       <c r="D4" s="3">
         <v>109263</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>8.0583376355188427</v>
       </c>
@@ -2387,7 +2381,7 @@
       <c r="D5" s="3">
         <v>96513</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>7.4326530612244897</v>
       </c>
@@ -2405,7 +2399,7 @@
       <c r="D6" s="3">
         <v>88982</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>7.3599669148056241</v>
       </c>
@@ -2423,7 +2417,7 @@
       <c r="D7" s="3">
         <v>98567</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>6.9267041461700636</v>
       </c>
@@ -2441,7 +2435,7 @@
       <c r="D8" s="3">
         <v>76919</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>6.7189902166317257</v>
       </c>
@@ -2459,7 +2453,7 @@
       <c r="D9" s="3">
         <v>63373</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>6.6933882551753277</v>
       </c>
@@ -2477,7 +2471,7 @@
       <c r="D10" s="3">
         <v>59076</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>6.9038214327451213</v>
       </c>
@@ -2495,7 +2489,7 @@
       <c r="D11" s="3">
         <v>70899</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>6.9542913192741542</v>
       </c>
@@ -2513,7 +2507,7 @@
       <c r="D12" s="3">
         <v>92394</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>7.4764525004045961</v>
       </c>
@@ -2531,7 +2525,7 @@
       <c r="D13" s="3">
         <v>95452</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>7.5141305203495241</v>
       </c>
@@ -2549,7 +2543,7 @@
       <c r="D14" s="3">
         <v>100325</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>7.6730401529636714</v>
       </c>
@@ -2567,7 +2561,7 @@
       <c r="D15" s="3">
         <v>89764</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>7.6355903368492681</v>
       </c>
@@ -2585,7 +2579,7 @@
       <c r="D16" s="3">
         <v>104351</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>7.9071758733045385</v>
       </c>
@@ -2603,7 +2597,7 @@
       <c r="D17" s="3">
         <v>76978</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>7.5225251636861135</v>
       </c>
@@ -2621,7 +2615,7 @@
       <c r="D18" s="3">
         <v>91341</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>7.4839000409668168</v>
       </c>
@@ -2639,7 +2633,7 @@
       <c r="D19" s="3">
         <v>84203</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>7.3649085979183067</v>
       </c>
@@ -2657,7 +2651,7 @@
       <c r="D20" s="3">
         <v>93851</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>7.0713532248342377</v>
       </c>
@@ -2676,7 +2670,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>8.9135833580594154E-2</v>
       </c>
@@ -2698,8 +2692,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2712,7 +2705,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -2732,7 +2725,7 @@
       <c r="D2" s="3">
         <v>518742</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>22.021650534895567</v>
       </c>
@@ -2750,7 +2743,7 @@
       <c r="D3" s="3">
         <v>466888</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>22.976771653543306</v>
       </c>
@@ -2768,7 +2761,7 @@
       <c r="D4" s="3">
         <v>518428</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>22.944368223058198</v>
       </c>
@@ -2786,7 +2779,7 @@
       <c r="D5" s="3">
         <v>977191</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>20.241336454212149</v>
       </c>
@@ -2804,7 +2797,7 @@
       <c r="D6" s="3">
         <v>529279</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>20.790282033152643</v>
       </c>
@@ -2822,7 +2815,7 @@
       <c r="D7" s="3">
         <v>1059598</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>19.396964870851409</v>
       </c>
@@ -2840,7 +2833,7 @@
       <c r="D8" s="3">
         <v>1022721</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>20.468338470159708</v>
       </c>
@@ -2858,7 +2851,7 @@
       <c r="D9" s="3">
         <v>522471</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>22.493154813156536</v>
       </c>
@@ -2876,7 +2869,7 @@
       <c r="D10" s="3">
         <v>519551</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>22.386720096518442</v>
       </c>
@@ -2894,7 +2887,7 @@
       <c r="D11" s="3">
         <v>629968</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>21.434773732562096</v>
       </c>
@@ -2912,7 +2905,7 @@
       <c r="D12" s="3">
         <v>667683</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>21.621858808290156</v>
       </c>
@@ -2930,7 +2923,7 @@
       <c r="D13" s="3">
         <v>623062</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>21.334817148335844</v>
       </c>
@@ -2948,7 +2941,7 @@
       <c r="D14" s="3">
         <v>605388</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>22.174572359986815</v>
       </c>
@@ -2966,7 +2959,7 @@
       <c r="D15" s="3">
         <v>593083</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>23.171830435631961</v>
       </c>
@@ -2984,7 +2977,7 @@
       <c r="D16" s="3">
         <v>607705</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>23.128639391056137</v>
       </c>
@@ -3002,7 +2995,7 @@
       <c r="D17" s="3">
         <v>591175</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>20.885148025153679</v>
       </c>
@@ -3020,7 +3013,7 @@
       <c r="D18" s="3">
         <v>618273</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>20.707113671377854</v>
       </c>
@@ -3038,7 +3031,7 @@
       <c r="D19" s="3">
         <v>507411</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>20.552940699935192</v>
       </c>
@@ -3056,7 +3049,7 @@
       <c r="D20" s="3">
         <v>624862</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>20.92008436840872</v>
       </c>
@@ -3075,7 +3068,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>7.8232579253991075E-2</v>
       </c>
@@ -3097,8 +3090,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3111,7 +3103,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -3131,7 +3123,7 @@
       <c r="D2" s="3">
         <v>1644016</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>25.013175912120012</v>
       </c>
@@ -3149,7 +3141,7 @@
       <c r="D3" s="3">
         <v>1556817</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>27.470655702992659</v>
       </c>
@@ -3167,7 +3159,7 @@
       <c r="D4" s="3">
         <v>2071431</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>29.769638699663705</v>
       </c>
@@ -3185,7 +3177,7 @@
       <c r="D5" s="3">
         <v>2290371</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>26.612107128333236</v>
       </c>
@@ -3203,7 +3195,7 @@
       <c r="D6" s="3">
         <v>1948796</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>25.515816486854508</v>
       </c>
@@ -3221,7 +3213,7 @@
       <c r="D7" s="3">
         <v>2287552</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>25.591837647953817</v>
       </c>
@@ -3239,7 +3231,7 @@
       <c r="D8" s="3">
         <v>2350506</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>25.34320247555177</v>
       </c>
@@ -3257,7 +3249,7 @@
       <c r="D9" s="3">
         <v>1690189</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>24.850969667563554</v>
       </c>
@@ -3275,7 +3267,7 @@
       <c r="D10" s="3">
         <v>1581770</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>24.592959980098883</v>
       </c>
@@ -3293,7 +3285,7 @@
       <c r="D11" s="3">
         <v>1924281</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>23.724629819132279</v>
       </c>
@@ -3311,7 +3303,7 @@
       <c r="D12" s="3">
         <v>2581069</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>21.192608649243375</v>
       </c>
@@ -3329,7 +3321,7 @@
       <c r="D13" s="3">
         <v>1801092</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>23.462716898546194</v>
       </c>
@@ -3347,7 +3339,7 @@
       <c r="D14" s="3">
         <v>1826377</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>24.933814796106432</v>
       </c>
@@ -3365,7 +3357,7 @@
       <c r="D15" s="3">
         <v>1495340</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>26.269060501721594</v>
       </c>
@@ -3383,7 +3375,7 @@
       <c r="D16" s="3">
         <v>1618685</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>27.417215738748961</v>
       </c>
@@ -3401,7 +3393,7 @@
       <c r="D17" s="3">
         <v>1791510</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>23.351581746373128</v>
       </c>
@@ -3419,7 +3411,7 @@
       <c r="D18" s="3">
         <v>2048535</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>23.623222666835801</v>
       </c>
@@ -3437,7 +3429,7 @@
       <c r="D19" s="3">
         <v>1083525</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>31.600705786280916</v>
       </c>
@@ -3455,7 +3447,7 @@
       <c r="D20" s="3">
         <v>1929701</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>22.188887739027447</v>
       </c>
@@ -3474,7 +3466,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>7.695023150025794E-2</v>
       </c>
@@ -3496,8 +3488,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3510,133 +3501,133 @@
         <v>45444</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="5"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45474</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="5"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45505</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="5"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45536</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45566</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45597</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45627</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45658</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45689</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="5"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45717</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45748</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45778</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="5"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45809</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45839</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45870</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45901</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45931</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45962</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45992</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -3648,7 +3639,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>

--- a/TPASS/TPASS表格.xlsx
+++ b/TPASS/TPASS表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\運籌\115\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\TPASS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9F10DF-0638-4BEE-93D9-F2096D326231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6DDE46-5634-4F62-8C1C-99994D4FD8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="24" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="25" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="花蓮縣TPASS年占比" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -238,10 +235,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
+    <numFmt numFmtId="179" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -294,15 +292,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1922,8 +1918,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1936,7 +1931,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -1956,7 +1951,7 @@
       <c r="D2" s="3">
         <v>391603</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>17.810660845044801</v>
       </c>
@@ -1974,7 +1969,7 @@
       <c r="D3" s="3">
         <v>303016</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>16.915982805783511</v>
       </c>
@@ -1992,7 +1987,7 @@
       <c r="D4" s="3">
         <v>414230</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>18.17276476265684</v>
       </c>
@@ -2010,7 +2005,7 @@
       <c r="D5" s="3">
         <v>568299</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>17.611298769717067</v>
       </c>
@@ -2028,7 +2023,7 @@
       <c r="D6" s="3">
         <v>526001</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>17.566743479277292</v>
       </c>
@@ -2046,7 +2041,7 @@
       <c r="D7" s="3">
         <v>528955</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>15.275355203881253</v>
       </c>
@@ -2064,7 +2059,7 @@
       <c r="D8" s="3">
         <v>628069</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>16.186928171954332</v>
       </c>
@@ -2082,7 +2077,7 @@
       <c r="D9" s="3">
         <v>282008</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>13.281589977864645</v>
       </c>
@@ -2100,7 +2095,7 @@
       <c r="D10" s="3">
         <v>294587</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>13.533651858317636</v>
       </c>
@@ -2118,7 +2113,7 @@
       <c r="D11" s="3">
         <v>381056</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>13.256888394099638</v>
       </c>
@@ -2136,7 +2131,7 @@
       <c r="D12" s="3">
         <v>381626</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>13.290127111265889</v>
       </c>
@@ -2154,7 +2149,7 @@
       <c r="D13" s="3">
         <v>330730</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>12.032233419434641</v>
       </c>
@@ -2172,7 +2167,7 @@
       <c r="D14" s="3">
         <v>345893</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>13.441089609077485</v>
       </c>
@@ -2190,7 +2185,7 @@
       <c r="D15" s="3">
         <v>255285</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>12.640374331550802</v>
       </c>
@@ -2208,7 +2203,7 @@
       <c r="D16" s="3">
         <v>279581</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>13.256567093409199</v>
       </c>
@@ -2226,7 +2221,7 @@
       <c r="D17" s="3">
         <v>401887</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>13.336220341795254</v>
       </c>
@@ -2244,7 +2239,7 @@
       <c r="D18" s="3">
         <v>402092</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>13.121394073880694</v>
       </c>
@@ -2262,7 +2257,7 @@
       <c r="D19" s="3">
         <v>305031</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>11.774985524030111</v>
       </c>
@@ -2280,7 +2275,7 @@
       <c r="D20" s="3">
         <v>339844</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>11.778055035696957</v>
       </c>
@@ -2299,7 +2294,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>3.7895103057209466E-2</v>
       </c>
@@ -2321,8 +2316,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2335,7 +2329,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -2355,7 +2349,7 @@
       <c r="D2" s="3">
         <v>82922</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>7.7374265186152842</v>
       </c>
@@ -2373,7 +2367,7 @@
       <c r="D3" s="3">
         <v>84740</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>7.9807873422490108</v>
       </c>
@@ -2391,7 +2385,7 @@
       <c r="D4" s="3">
         <v>109263</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>8.0583376355188427</v>
       </c>
@@ -2409,7 +2403,7 @@
       <c r="D5" s="3">
         <v>96513</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>7.4326530612244897</v>
       </c>
@@ -2427,7 +2421,7 @@
       <c r="D6" s="3">
         <v>88982</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>7.3599669148056241</v>
       </c>
@@ -2445,7 +2439,7 @@
       <c r="D7" s="3">
         <v>98567</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>6.9267041461700636</v>
       </c>
@@ -2463,7 +2457,7 @@
       <c r="D8" s="3">
         <v>76919</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>6.7189902166317257</v>
       </c>
@@ -2481,7 +2475,7 @@
       <c r="D9" s="3">
         <v>63373</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>6.6933882551753277</v>
       </c>
@@ -2499,7 +2493,7 @@
       <c r="D10" s="3">
         <v>59076</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>6.9038214327451213</v>
       </c>
@@ -2517,7 +2511,7 @@
       <c r="D11" s="3">
         <v>70899</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>6.9542913192741542</v>
       </c>
@@ -2535,7 +2529,7 @@
       <c r="D12" s="3">
         <v>92394</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>7.4764525004045961</v>
       </c>
@@ -2553,7 +2547,7 @@
       <c r="D13" s="3">
         <v>95452</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>7.5141305203495241</v>
       </c>
@@ -2571,7 +2565,7 @@
       <c r="D14" s="3">
         <v>100325</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>7.6730401529636714</v>
       </c>
@@ -2589,7 +2583,7 @@
       <c r="D15" s="3">
         <v>89764</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>7.6355903368492681</v>
       </c>
@@ -2607,7 +2601,7 @@
       <c r="D16" s="3">
         <v>104351</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>7.9071758733045385</v>
       </c>
@@ -2625,7 +2619,7 @@
       <c r="D17" s="3">
         <v>76978</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>7.5225251636861135</v>
       </c>
@@ -2643,7 +2637,7 @@
       <c r="D18" s="3">
         <v>91341</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>7.4839000409668168</v>
       </c>
@@ -2661,7 +2655,7 @@
       <c r="D19" s="3">
         <v>84203</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>7.3649085979183067</v>
       </c>
@@ -2679,7 +2673,7 @@
       <c r="D20" s="3">
         <v>93851</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>7.0713532248342377</v>
       </c>
@@ -2698,7 +2692,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>8.9135833580594154E-2</v>
       </c>
@@ -2720,8 +2714,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2734,7 +2727,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -2754,7 +2747,7 @@
       <c r="D2" s="3">
         <v>518742</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>22.021650534895567</v>
       </c>
@@ -2772,7 +2765,7 @@
       <c r="D3" s="3">
         <v>466888</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>22.976771653543306</v>
       </c>
@@ -2790,7 +2783,7 @@
       <c r="D4" s="3">
         <v>518428</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>22.944368223058198</v>
       </c>
@@ -2808,7 +2801,7 @@
       <c r="D5" s="3">
         <v>977191</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>20.241336454212149</v>
       </c>
@@ -2826,7 +2819,7 @@
       <c r="D6" s="3">
         <v>529279</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>20.790282033152643</v>
       </c>
@@ -2844,7 +2837,7 @@
       <c r="D7" s="3">
         <v>1059598</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>19.396964870851409</v>
       </c>
@@ -2862,7 +2855,7 @@
       <c r="D8" s="3">
         <v>1022721</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>20.468338470159708</v>
       </c>
@@ -2880,7 +2873,7 @@
       <c r="D9" s="3">
         <v>522471</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>22.493154813156536</v>
       </c>
@@ -2898,7 +2891,7 @@
       <c r="D10" s="3">
         <v>519551</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>22.386720096518442</v>
       </c>
@@ -2916,7 +2909,7 @@
       <c r="D11" s="3">
         <v>629968</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>21.434773732562096</v>
       </c>
@@ -2934,7 +2927,7 @@
       <c r="D12" s="3">
         <v>667683</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>21.621858808290156</v>
       </c>
@@ -2952,7 +2945,7 @@
       <c r="D13" s="3">
         <v>623062</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>21.334817148335844</v>
       </c>
@@ -2970,7 +2963,7 @@
       <c r="D14" s="3">
         <v>605388</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>22.174572359986815</v>
       </c>
@@ -2988,7 +2981,7 @@
       <c r="D15" s="3">
         <v>593083</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>23.171830435631961</v>
       </c>
@@ -3006,7 +2999,7 @@
       <c r="D16" s="3">
         <v>607705</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>23.128639391056137</v>
       </c>
@@ -3024,7 +3017,7 @@
       <c r="D17" s="3">
         <v>591175</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>20.885148025153679</v>
       </c>
@@ -3042,7 +3035,7 @@
       <c r="D18" s="3">
         <v>618273</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>20.707113671377854</v>
       </c>
@@ -3060,7 +3053,7 @@
       <c r="D19" s="3">
         <v>507411</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>20.552940699935192</v>
       </c>
@@ -3078,7 +3071,7 @@
       <c r="D20" s="3">
         <v>624862</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>20.92008436840872</v>
       </c>
@@ -3097,7 +3090,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>7.8232579253991075E-2</v>
       </c>
@@ -3119,8 +3112,7 @@
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3133,7 +3125,7 @@
       <c r="C1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -3153,7 +3145,7 @@
       <c r="D2" s="3">
         <v>1644016</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>D2/C2</f>
         <v>25.013175912120012</v>
       </c>
@@ -3171,7 +3163,7 @@
       <c r="D3" s="3">
         <v>1556817</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <f t="shared" ref="E3:E20" si="0">D3/C3</f>
         <v>27.470655702992659</v>
       </c>
@@ -3189,7 +3181,7 @@
       <c r="D4" s="3">
         <v>2071431</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <f t="shared" si="0"/>
         <v>29.769638699663705</v>
       </c>
@@ -3207,7 +3199,7 @@
       <c r="D5" s="3">
         <v>2290371</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>26.612107128333236</v>
       </c>
@@ -3225,7 +3217,7 @@
       <c r="D6" s="3">
         <v>1948796</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>25.515816486854508</v>
       </c>
@@ -3243,7 +3235,7 @@
       <c r="D7" s="3">
         <v>2287552</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>25.591837647953817</v>
       </c>
@@ -3261,7 +3253,7 @@
       <c r="D8" s="3">
         <v>2350506</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>25.34320247555177</v>
       </c>
@@ -3279,7 +3271,7 @@
       <c r="D9" s="3">
         <v>1690189</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>24.850969667563554</v>
       </c>
@@ -3297,7 +3289,7 @@
       <c r="D10" s="3">
         <v>1581770</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>24.592959980098883</v>
       </c>
@@ -3315,7 +3307,7 @@
       <c r="D11" s="3">
         <v>1924281</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>23.724629819132279</v>
       </c>
@@ -3333,7 +3325,7 @@
       <c r="D12" s="3">
         <v>2581069</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>21.192608649243375</v>
       </c>
@@ -3351,7 +3343,7 @@
       <c r="D13" s="3">
         <v>1801092</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>23.462716898546194</v>
       </c>
@@ -3369,7 +3361,7 @@
       <c r="D14" s="3">
         <v>1826377</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>24.933814796106432</v>
       </c>
@@ -3387,7 +3379,7 @@
       <c r="D15" s="3">
         <v>1495340</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>26.269060501721594</v>
       </c>
@@ -3405,7 +3397,7 @@
       <c r="D16" s="3">
         <v>1618685</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>27.417215738748961</v>
       </c>
@@ -3423,7 +3415,7 @@
       <c r="D17" s="3">
         <v>1791510</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>23.351581746373128</v>
       </c>
@@ -3441,7 +3433,7 @@
       <c r="D18" s="3">
         <v>2048535</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>23.623222666835801</v>
       </c>
@@ -3459,7 +3451,7 @@
       <c r="D19" s="3">
         <v>1083525</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>31.600705786280916</v>
       </c>
@@ -3477,7 +3469,7 @@
       <c r="D20" s="3">
         <v>1929701</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>22.188887739027447</v>
       </c>
@@ -3496,7 +3488,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <f>(B21-C21)/B21</f>
         <v>7.695023150025794E-2</v>
       </c>
@@ -3516,11 +3508,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
@@ -3530,18 +3522,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -3550,21 +3542,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>6042</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.48534018796690498</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>5442</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.43714354566631858</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>965</v>
       </c>
       <c r="G2" s="1">
@@ -3584,21 +3576,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>4778</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.47537558451895334</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>4321</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.42990747189334394</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>952</v>
       </c>
       <c r="G3" s="1">
@@ -3618,21 +3610,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>5564</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.47405640282866152</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>4871</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.41501235409389109</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>1302</v>
       </c>
       <c r="G4" s="1">
@@ -3652,21 +3644,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>8545</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.48540104521699612</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>7532</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.42785730515791864</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>1527</v>
       </c>
       <c r="G5" s="1">
@@ -3686,21 +3678,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>7870</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.47775147210587021</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>7367</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.44721665756085716</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>1236</v>
       </c>
       <c r="G6" s="1">
@@ -3720,21 +3712,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>9189</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.49937503396554533</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>8042</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.43704146513776426</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>1170</v>
       </c>
       <c r="G7" s="1">
@@ -3754,21 +3746,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>9985</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.49865161805833003</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>8688</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.4338793447862565</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>1351</v>
       </c>
       <c r="G8" s="1">
@@ -3788,21 +3780,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>7178</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.57040686586141132</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>4863</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.38644310235219326</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>543</v>
       </c>
       <c r="G9" s="1">
@@ -3822,21 +3814,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>7084</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.55391351943076084</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>5136</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.40159512080694348</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>569</v>
       </c>
       <c r="G10" s="1">
@@ -3856,21 +3848,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>8855</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.52408854166666663</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>7362</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.43572443181818182</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>679</v>
       </c>
       <c r="G11" s="1">
@@ -3890,21 +3882,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>9290</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.54605301828013875</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>7001</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.41150884617645328</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>722</v>
       </c>
       <c r="G12" s="1">
@@ -3924,21 +3916,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>9336</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.54824123553937398</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>7157</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.42028304656761994</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>536</v>
       </c>
       <c r="G13" s="1">
@@ -3958,21 +3950,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>8133</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.54209158168366323</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>6122</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.4080517229887356</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>748</v>
       </c>
       <c r="G14" s="1">
@@ -3992,21 +3984,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>6649</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.5671272603207097</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>4439</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.37862504264756058</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>636</v>
       </c>
       <c r="G15" s="1">
@@ -4026,21 +4018,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>6280</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.53220338983050852</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>4653</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.39432203389830506</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>867</v>
       </c>
       <c r="G16" s="1">
@@ -4060,21 +4052,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>8606</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.48961711327302726</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>8056</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.45832622176708199</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>915</v>
       </c>
       <c r="G17" s="1">
@@ -4094,21 +4086,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>9398</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.5075884418039428</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>8280</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.44720496894409939</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>837</v>
       </c>
       <c r="G18" s="1">
@@ -4128,21 +4120,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>9373</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.54672188520765286</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>7653</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.4463952403173122</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>118</v>
       </c>
       <c r="G19" s="1">
@@ -4162,21 +4154,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>10537</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.54624157594608602</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>8636</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.44769310523587352</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>117</v>
       </c>
       <c r="G20" s="1">
@@ -4193,10 +4185,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4309,11 +4301,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -4323,18 +4315,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -4343,21 +4335,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>968</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.45811642214860387</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>1139</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.53904401325130147</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>6</v>
       </c>
       <c r="G2" s="1">
@@ -4377,21 +4369,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>605</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.37093807480073576</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>1023</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.62722256284488043</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>3</v>
       </c>
       <c r="G3" s="1">
@@ -4411,21 +4403,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>725</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.4205336426914153</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>993</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.57598607888631093</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>6</v>
       </c>
       <c r="G4" s="1">
@@ -4445,21 +4437,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>1536</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.45309734513274336</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>1846</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.54454277286135688</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>8</v>
       </c>
       <c r="G5" s="1">
@@ -4479,21 +4471,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>1543</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.42146954384048074</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>2107</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.57552581261950286</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>11</v>
       </c>
       <c r="G6" s="1">
@@ -4513,21 +4505,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>1761</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.42382671480144407</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>2382</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.57328519855595672</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>12</v>
       </c>
       <c r="G7" s="1">
@@ -4547,21 +4539,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>2039</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.42971548998946257</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>2689</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.56670179135932564</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>17</v>
       </c>
       <c r="G8" s="1">
@@ -4581,21 +4573,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>1064</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.4172549019607843</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>1480</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.58039215686274515</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>6</v>
       </c>
       <c r="G9" s="1">
@@ -4615,21 +4607,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>1351</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.40053364957011561</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>2012</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.59650163059590866</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>10</v>
       </c>
       <c r="G10" s="1">
@@ -4649,21 +4641,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>1992</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.38270893371757925</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>3197</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.61421709894332377</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>16</v>
       </c>
       <c r="G11" s="1">
@@ -4683,21 +4675,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>1976</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.41573742899221544</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>2765</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.58173784977908694</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>12</v>
       </c>
       <c r="G12" s="1">
@@ -4717,21 +4709,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>1987</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.39771817453963171</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>2993</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.59907926341072859</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>16</v>
       </c>
       <c r="G13" s="1">
@@ -4751,21 +4743,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>1679</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.41051344743276286</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>2397</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.58606356968215156</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>14</v>
       </c>
       <c r="G14" s="1">
@@ -4785,21 +4777,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>1063</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.39782934131736525</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>1597</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.59767964071856283</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>12</v>
       </c>
       <c r="G15" s="1">
@@ -4819,21 +4811,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>570</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.25232403718459495</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>1605</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.71049136786188583</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>84</v>
       </c>
       <c r="G16" s="1">
@@ -4853,21 +4845,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>1545</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.2911249293386094</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>3564</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.67156585641605426</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>198</v>
       </c>
       <c r="G17" s="1">
@@ -4887,21 +4879,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>1698</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.28380411164967406</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>4078</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.68159786060504768</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>207</v>
       </c>
       <c r="G18" s="1">
@@ -4921,21 +4913,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>2381</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.41058803241938263</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>3402</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.58665287118468701</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>16</v>
       </c>
       <c r="G19" s="1">
@@ -4955,21 +4947,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>2730</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.41807044410413474</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>3776</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.57825421133231236</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>24</v>
       </c>
       <c r="G20" s="1">
@@ -4986,10 +4978,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5008,11 +5000,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -5022,18 +5014,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -5042,21 +5034,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>3826</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.58780150560762023</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>2422</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.37210016899677367</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>261</v>
       </c>
       <c r="G2" s="1">
@@ -5076,21 +5068,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>3893</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.6033787972721637</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>2356</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.3651580905145691</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>203</v>
       </c>
       <c r="G3" s="1">
@@ -5110,21 +5102,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>5025</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.60201269917335565</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>3035</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.36360368994848447</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>287</v>
       </c>
       <c r="G4" s="1">
@@ -5144,21 +5136,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>3900</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.552956188855806</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>2808</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.39812845597618035</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>345</v>
       </c>
       <c r="G5" s="1">
@@ -5178,21 +5170,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>3631</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.55266362252663626</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>2580</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.39269406392694062</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>359</v>
       </c>
       <c r="G6" s="1">
@@ -5212,21 +5204,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>3888</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.51171360884443273</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>3250</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.4277441431955778</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>460</v>
       </c>
       <c r="G7" s="1">
@@ -5246,21 +5238,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>3278</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.54460873899318829</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>2358</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.39175942847649109</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>383</v>
       </c>
       <c r="G8" s="1">
@@ -5280,21 +5272,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>3039</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.57393767705382437</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>1956</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.36940509915014164</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>300</v>
       </c>
       <c r="G9" s="1">
@@ -5314,21 +5306,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>2766</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.57397800373521479</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>1741</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.36127827350072628</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>312</v>
       </c>
       <c r="G10" s="1">
@@ -5348,21 +5340,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>3243</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.57571453932185335</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>2070</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.36747736552458726</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>320</v>
       </c>
       <c r="G11" s="1">
@@ -5382,21 +5374,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>3964</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.56306818181818186</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>2757</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.39161931818181817</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>319</v>
       </c>
       <c r="G12" s="1">
@@ -5416,21 +5408,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>4355</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.5863740406624478</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>2752</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.37053992190655716</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>320</v>
       </c>
       <c r="G13" s="1">
@@ -5450,21 +5442,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>4331</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.57356641504436501</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>2895</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.38339292808899483</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>325</v>
       </c>
       <c r="G14" s="1">
@@ -5484,21 +5476,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>4293</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.60176619007569387</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>2585</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.36234931314830388</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>256</v>
       </c>
       <c r="G15" s="1">
@@ -5518,21 +5510,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>4761</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.58901397995793636</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>3083</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.38141779042434737</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>239</v>
       </c>
       <c r="G16" s="1">
@@ -5552,21 +5544,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>3357</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.57140425531914896</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>2182</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.37140425531914895</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>336</v>
       </c>
       <c r="G17" s="1">
@@ -5586,21 +5578,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>3888</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.55519063258603452</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>2745</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.39197486791375125</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>370</v>
       </c>
       <c r="G18" s="1">
@@ -5620,21 +5612,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>3161</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.56537292076551604</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>2148</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.38418887497764265</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>282</v>
       </c>
       <c r="G19" s="1">
@@ -5654,21 +5646,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>3754</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.57869585324495143</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>2414</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.37212887313087711</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>319</v>
       </c>
       <c r="G20" s="1">
@@ -5685,10 +5677,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5707,11 +5699,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -5721,18 +5713,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -5741,21 +5733,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>77</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.35813953488372091</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>52</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.24186046511627907</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>86</v>
       </c>
       <c r="G2" s="1">
@@ -5775,21 +5767,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>54</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.33750000000000002</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>59</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.36875000000000002</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>47</v>
       </c>
       <c r="G3" s="1">
@@ -5809,21 +5801,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>96</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.41921397379912662</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>83</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.36244541484716158</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>50</v>
       </c>
       <c r="G4" s="1">
@@ -5843,21 +5835,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>82</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.26973684210526316</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>89</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.29276315789473684</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>133</v>
       </c>
       <c r="G5" s="1">
@@ -5877,21 +5869,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>100</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.33112582781456956</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>75</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.24834437086092714</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>127</v>
       </c>
       <c r="G6" s="1">
@@ -5911,21 +5903,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>89</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.27051671732522797</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>102</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.3100303951367781</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>138</v>
       </c>
       <c r="G7" s="1">
@@ -5945,21 +5937,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>87</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.28155339805825241</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>84</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.27184466019417475</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>138</v>
       </c>
       <c r="G8" s="1">
@@ -5979,21 +5971,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>86</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.2986111111111111</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>85</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.2951388888888889</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>117</v>
       </c>
       <c r="G9" s="1">
@@ -6013,21 +6005,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>82</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.27424749163879597</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>102</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.34113712374581939</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>115</v>
       </c>
       <c r="G10" s="1">
@@ -6047,21 +6039,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>84</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.27722772277227725</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>83</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.27392739273927391</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>136</v>
       </c>
       <c r="G11" s="1">
@@ -6081,21 +6073,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>91</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.26923076923076922</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>115</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.34023668639053256</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>132</v>
       </c>
       <c r="G12" s="1">
@@ -6115,21 +6107,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>102</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.28099173553719009</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>123</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.33884297520661155</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>138</v>
       </c>
       <c r="G13" s="1">
@@ -6149,21 +6141,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>95</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.26243093922651933</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>128</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.35359116022099446</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>139</v>
       </c>
       <c r="G14" s="1">
@@ -6183,21 +6175,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>98</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.33793103448275863</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>115</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.39655172413793105</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>77</v>
       </c>
       <c r="G15" s="1">
@@ -6217,21 +6209,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>138</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.39316239316239315</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>142</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.40455840455840458</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>71</v>
       </c>
       <c r="G16" s="1">
@@ -6251,21 +6243,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>40</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.10666666666666667</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>171</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.45600000000000002</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>164</v>
       </c>
       <c r="G17" s="1">
@@ -6285,21 +6277,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>44</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.10918114143920596</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>176</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.43672456575682383</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>183</v>
       </c>
       <c r="G18" s="1">
@@ -6319,21 +6311,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>108</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.3323076923076923</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>110</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.33846153846153848</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>107</v>
       </c>
       <c r="G19" s="1">
@@ -6353,21 +6345,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>98</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.29696969696969699</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>114</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.34545454545454546</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>118</v>
       </c>
       <c r="G20" s="1">
@@ -6384,10 +6376,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6406,11 +6398,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -6420,18 +6412,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -6440,21 +6432,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>3945</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.48016066212268743</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>3056</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.37195715676728336</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>1215</v>
       </c>
       <c r="G2" s="1">
@@ -6474,21 +6466,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>3941</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.47920719844357978</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>3124</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.37986381322957197</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>1159</v>
       </c>
       <c r="G3" s="1">
@@ -6508,21 +6500,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>4728</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.50926324859974148</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>3377</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.36374407582938389</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>1179</v>
       </c>
       <c r="G4" s="1">
@@ -6542,21 +6534,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>1289</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.14410285075461152</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>5470</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.61151481274455</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>2186</v>
       </c>
       <c r="G5" s="1">
@@ -6576,21 +6568,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>4310</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.47155361050328226</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>3611</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.39507658643326038</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>1219</v>
       </c>
       <c r="G6" s="1">
@@ -6610,21 +6602,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>1412</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.1226013718850395</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>7440</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.64600156290700705</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>2665</v>
       </c>
       <c r="G7" s="1">
@@ -6644,21 +6636,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>1373</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.1346738597351643</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>6381</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.62589504659146644</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>2441</v>
       </c>
       <c r="G8" s="1">
@@ -6678,21 +6670,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>4986</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.53705299439896592</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>3164</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.34080137871607064</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>1134</v>
       </c>
       <c r="G9" s="1">
@@ -6712,21 +6704,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>4456</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.53403643336529238</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>2726</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.32670182166826461</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>1162</v>
       </c>
       <c r="G10" s="1">
@@ -6746,21 +6738,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>4467</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.4920687376074025</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>3226</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.35536461775721523</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>1385</v>
       </c>
       <c r="G11" s="1">
@@ -6780,21 +6772,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>4508</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.45627530364372471</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>3954</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.40020242914979759</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>1418</v>
       </c>
       <c r="G12" s="1">
@@ -6814,21 +6806,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>4758</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.51717391304347826</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>3117</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.33880434782608698</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>1325</v>
       </c>
       <c r="G13" s="1">
@@ -6848,21 +6840,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>4466</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.50338142470694314</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>3166</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.35685302073940489</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>1240</v>
       </c>
       <c r="G14" s="1">
@@ -6882,21 +6874,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>4805</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.51302583813794578</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>3412</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.36429639120222079</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>1149</v>
       </c>
       <c r="G15" s="1">
@@ -6916,21 +6908,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>5181</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.50374331550802143</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>3944</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.38347107438016531</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>1160</v>
       </c>
       <c r="G16" s="1">
@@ -6950,21 +6942,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>4193</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.47821624087591241</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>3240</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.36952554744525545</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>1335</v>
       </c>
       <c r="G17" s="1">
@@ -6984,21 +6976,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>4828</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.5100898045430533</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>3302</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.34886423666138405</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>1335</v>
       </c>
       <c r="G18" s="1">
@@ -7018,21 +7010,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>3679</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.48844928305894847</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>2690</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.35714285714285715</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>1163</v>
       </c>
       <c r="G19" s="1">
@@ -7052,21 +7044,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>4412</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.49104062326099052</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>3229</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.35937673900946021</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>1344</v>
       </c>
       <c r="G20" s="1">
@@ -7083,10 +7075,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7105,11 +7097,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -7119,18 +7111,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -7139,21 +7131,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>152</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.24796084828711257</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>194</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.31647634584013051</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>267</v>
       </c>
       <c r="G2" s="1">
@@ -7173,21 +7165,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>145</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.28265107212475632</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>154</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.30019493177387913</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>214</v>
       </c>
       <c r="G3" s="1">
@@ -7207,21 +7199,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>187</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.31270903010033446</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>207</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.34615384615384615</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>204</v>
       </c>
       <c r="G4" s="1">
@@ -7241,21 +7233,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>164</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.23462088698140202</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>181</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.25894134477825465</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>354</v>
       </c>
       <c r="G5" s="1">
@@ -7275,21 +7267,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>186</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.27761194029850744</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>193</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.28805970149253729</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>291</v>
       </c>
       <c r="G6" s="1">
@@ -7309,21 +7301,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>183</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.25811001410437234</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>173</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.24400564174894218</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>353</v>
       </c>
       <c r="G7" s="1">
@@ -7343,21 +7335,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>160</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.22598870056497175</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>184</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.25988700564971751</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>364</v>
       </c>
       <c r="G8" s="1">
@@ -7377,21 +7369,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>199</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.29657228017883758</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>224</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.33383010432190763</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>248</v>
       </c>
       <c r="G9" s="1">
@@ -7411,21 +7403,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>198</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.29508196721311475</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>195</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.29061102831594637</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>278</v>
       </c>
       <c r="G10" s="1">
@@ -7445,21 +7437,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>189</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.26359832635983266</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>207</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.28870292887029286</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>321</v>
       </c>
       <c r="G11" s="1">
@@ -7479,21 +7471,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>119</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.16368638239339753</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>272</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.37414030261348008</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>336</v>
       </c>
       <c r="G12" s="1">
@@ -7513,21 +7505,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>188</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.26038781163434904</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>212</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.29362880886426596</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>322</v>
       </c>
       <c r="G13" s="1">
@@ -7547,21 +7539,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>216</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.29268292682926828</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>250</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.33875338753387535</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>272</v>
       </c>
       <c r="G14" s="1">
@@ -7581,21 +7573,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>189</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.28083209509658247</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>226</v>
       </c>
       <c r="E15" s="1">
         <f>D15/I15</f>
         <v>0.33580980683506684</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>258</v>
       </c>
       <c r="G15" s="1">
@@ -7615,21 +7607,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>248</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.35683453237410073</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>224</v>
       </c>
       <c r="E16" s="1">
         <f>D16/I16</f>
         <v>0.32230215827338127</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>223</v>
       </c>
       <c r="G16" s="1">
@@ -7649,21 +7641,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>185</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.24601063829787234</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>219</v>
       </c>
       <c r="E17" s="1">
         <f>D17/I17</f>
         <v>0.29122340425531917</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>348</v>
       </c>
       <c r="G17" s="1">
@@ -7683,21 +7675,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>236</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.29499999999999998</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>237</v>
       </c>
       <c r="E18" s="1">
         <f>D18/I18</f>
         <v>0.29625000000000001</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>327</v>
       </c>
       <c r="G18" s="1">
@@ -7717,21 +7709,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>172</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.25481481481481483</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>174</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.25777777777777777</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>329</v>
       </c>
       <c r="G19" s="1">
@@ -7751,21 +7743,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>267</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.31191588785046731</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>240</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.28037383177570091</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>349</v>
       </c>
       <c r="G20" s="1">
@@ -7782,10 +7774,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7804,11 +7796,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -7818,18 +7810,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -7838,21 +7830,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>5461</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>0.34925812228191355</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>6402</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.40943975441289332</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>3773</v>
       </c>
       <c r="G2" s="1">
@@ -7872,21 +7864,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>5761</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>0.36910558687852385</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>6338</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.40607380830343415</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>3509</v>
       </c>
       <c r="G3" s="1">
@@ -7906,21 +7898,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>6674</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.3685256764218664</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>6724</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.37128658199889564</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>4712</v>
       </c>
       <c r="G4" s="1">
@@ -7940,21 +7932,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>4588</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.26572454534924128</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>7065</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.40918568284489748</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>5613</v>
       </c>
       <c r="G5" s="1">
@@ -7974,21 +7966,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>5266</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>0.3186494009439671</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>6689</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.40475614183710518</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>4571</v>
       </c>
       <c r="G6" s="1">
@@ -8008,21 +8000,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>5014</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.25471170942341886</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>9299</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.47239014478028957</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>5372</v>
       </c>
       <c r="G7" s="1">
@@ -8042,21 +8034,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>5057</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.27320367368989734</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>8160</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.44084278768233387</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>5293</v>
       </c>
       <c r="G8" s="1">
@@ -8076,21 +8068,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>6286</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>0.37405534067241891</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>6645</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.39541803034811068</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>3874</v>
       </c>
       <c r="G9" s="1">
@@ -8110,21 +8102,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>5671</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>0.36371216008209339</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>6144</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.39404822986146743</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>3777</v>
       </c>
       <c r="G10" s="1">
@@ -8144,21 +8136,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>5445</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>0.33170880292415472</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>6579</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.40079195857447458</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>4391</v>
       </c>
       <c r="G11" s="1">
@@ -8178,21 +8170,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>3609</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>0.20863683662851196</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>8135</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.47028558214822525</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>5554</v>
       </c>
       <c r="G12" s="1">
@@ -8212,21 +8204,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>5399</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>0.34142793903750079</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>6258</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.39575033200531207</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>4156</v>
       </c>
       <c r="G13" s="1">
@@ -8246,21 +8238,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>5534</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>0.35003162555344719</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>6094</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.38545224541429474</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>4182</v>
       </c>
       <c r="G14" s="1">
@@ -8280,21 +8272,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>5974</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.38262985973227437</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>6319</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.40472683020559791</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>3320</v>
       </c>
       <c r="G15" s="1">
@@ -8314,21 +8306,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>6817</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.39216475867226602</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>7057</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.40597135132025541</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>3509</v>
       </c>
       <c r="G16" s="1">
@@ -8348,21 +8340,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>4777</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>0.33141390314971553</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>5459</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.37872901345913695</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>4178</v>
       </c>
       <c r="G17" s="1">
@@ -8382,21 +8374,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>5361</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>0.32175009002520705</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>6694</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.40175249069739527</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>4607</v>
       </c>
       <c r="G18" s="1">
@@ -8416,21 +8408,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>3574</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.38966419537723507</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>3550</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.38704753597906671</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>2048</v>
       </c>
       <c r="G19" s="1">
@@ -8450,21 +8442,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>5882</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>0.34295376362894292</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>6907</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.40271704273803277</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>4362</v>
       </c>
       <c r="G20" s="1">
@@ -8481,10 +8473,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8503,11 +8495,11 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -8517,18 +8509,18 @@
       <c r="A1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
       <c r="I1" t="s">
         <v>2</v>
       </c>
@@ -8537,21 +8529,21 @@
       <c r="A2" s="2">
         <v>45444</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>103</v>
       </c>
       <c r="C2" s="1">
         <f>B2/I2</f>
         <v>7.4637681159420294E-2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>335</v>
       </c>
       <c r="E2" s="1">
         <f>D2/I2</f>
         <v>0.24275362318840579</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>942</v>
       </c>
       <c r="G2" s="1">
@@ -8571,21 +8563,21 @@
       <c r="A3" s="2">
         <v>45474</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>119</v>
       </c>
       <c r="C3" s="1">
         <f>B3/I3</f>
         <v>9.6905537459283389E-2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="8">
         <v>383</v>
       </c>
       <c r="E3" s="1">
         <f>D3/I3</f>
         <v>0.31188925081433228</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="8">
         <v>726</v>
       </c>
       <c r="G3" s="1">
@@ -8605,21 +8597,21 @@
       <c r="A4" s="2">
         <v>45505</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>212</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" ref="C4:C20" si="0">B4/I4</f>
         <v>0.15024805102763997</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>436</v>
       </c>
       <c r="E4" s="1">
         <f t="shared" ref="E4:E20" si="1">D4/I4</f>
         <v>0.30900070871722185</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>763</v>
       </c>
       <c r="G4" s="1">
@@ -8639,21 +8631,21 @@
       <c r="A5" s="2">
         <v>45536</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>123</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>6.8676716917922945E-2</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>355</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="1"/>
         <v>0.19821328866554996</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>1313</v>
       </c>
       <c r="G5" s="1">
@@ -8673,21 +8665,21 @@
       <c r="A6" s="2">
         <v>45566</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>147</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>8.2445316881660125E-2</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>380</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
         <v>0.2131239484015704</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>1256</v>
       </c>
       <c r="G6" s="1">
@@ -8707,21 +8699,21 @@
       <c r="A7" s="2">
         <v>45597</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>116</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>6.1473237943826177E-2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>411</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>0.21780604133545309</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>1360</v>
       </c>
       <c r="G7" s="1">
@@ -8741,21 +8733,21 @@
       <c r="A8" s="2">
         <v>45627</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>101</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>5.3185887309110058E-2</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>379</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>0.19957872564507637</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="7">
         <v>1419</v>
       </c>
       <c r="G8" s="1">
@@ -8775,21 +8767,21 @@
       <c r="A9" s="2">
         <v>45658</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>137</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>7.6579094466182218E-2</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>424</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>0.23700391280044716</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>1228</v>
       </c>
       <c r="G9" s="1">
@@ -8809,21 +8801,21 @@
       <c r="A10" s="2">
         <v>45689</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>151</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>8.305830583058306E-2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>438</v>
       </c>
       <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>0.24092409240924093</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>1229</v>
       </c>
       <c r="G10" s="1">
@@ -8843,21 +8835,21 @@
       <c r="A11" s="2">
         <v>45717</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>147</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>7.4733096085409248E-2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="8">
         <v>377</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
         <v>0.19166243009659381</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>1443</v>
       </c>
       <c r="G11" s="1">
@@ -8877,21 +8869,21 @@
       <c r="A12" s="2">
         <v>45748</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>97</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>5.0811943425877422E-2</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="8">
         <v>381</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
         <v>0.1995809324253536</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>1431</v>
       </c>
       <c r="G12" s="1">
@@ -8911,21 +8903,21 @@
       <c r="A13" s="2">
         <v>45778</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>118</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>6.0450819672131145E-2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="8">
         <v>387</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
         <v>0.19825819672131148</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>1447</v>
       </c>
       <c r="G13" s="1">
@@ -8945,21 +8937,21 @@
       <c r="A14" s="2">
         <v>45809</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>159</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>8.0833756990340622E-2</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="8">
         <v>502</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="1"/>
         <v>0.25521098118962887</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>1306</v>
       </c>
       <c r="G14" s="1">
@@ -8979,21 +8971,21 @@
       <c r="A15" s="2">
         <v>45839</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>206</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>0.12402167369054787</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="8">
         <v>546</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
         <v>0.32871763997591813</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>909</v>
       </c>
       <c r="G15" s="1">
@@ -9013,21 +9005,21 @@
       <c r="A16" s="2">
         <v>45870</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>197</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>0.11932162325863113</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="8">
         <v>563</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
         <v>0.3410054512416717</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>891</v>
       </c>
       <c r="G16" s="1">
@@ -9047,21 +9039,21 @@
       <c r="A17" s="2">
         <v>45901</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>172</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>8.0903104421448727E-2</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="8">
         <v>484</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="1"/>
         <v>0.22765757290686736</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="7">
         <v>1470</v>
       </c>
       <c r="G17" s="1">
@@ -9081,21 +9073,21 @@
       <c r="A18" s="2">
         <v>45931</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>165</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>7.395786642761093E-2</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="8">
         <v>492</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
         <v>0.22052891080233078</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>1574</v>
       </c>
       <c r="G18" s="1">
@@ -9115,21 +9107,21 @@
       <c r="A19" s="2">
         <v>45962</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>187</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>0.15178571428571427</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="8">
         <v>410</v>
       </c>
       <c r="E19" s="1">
         <f t="shared" si="1"/>
         <v>0.33279220779220781</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="7">
         <v>635</v>
       </c>
       <c r="G19" s="1">
@@ -9149,21 +9141,21 @@
       <c r="A20" s="2">
         <v>45992</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>186</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>8.1364829396325458E-2</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="8">
         <v>485</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="1"/>
         <v>0.21216097987751531</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>1615</v>
       </c>
       <c r="G20" s="1">
@@ -9180,10 +9172,10 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="3"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
